--- a/ig/DM-AVRIL-2026/ValueSet-jdv-modalite-entree-esms-cisis.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-jdv-modalite-entree-esms-cisis.xlsx
@@ -9,13 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -101,6 +100,12 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>ORG-227</t>
+  </si>
+  <si>
+    <t>Domicile ou milieu ordinaire</t>
+  </si>
+  <si>
     <t>ORG-228</t>
   </si>
   <si>
@@ -128,13 +133,7 @@
     <t>Etablissement de Soins Médicaux</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
-  </si>
-  <si>
-    <t>ORG-227</t>
-  </si>
-  <si>
-    <t>Domicile ou milieu ordinaire</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice</t>
   </si>
 </sst>
 </file>
@@ -398,7 +397,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -434,15 +433,23 @@
         <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -469,72 +476,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s" s="2">
         <v>39</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
